--- a/artfynd/A 26849-2026 artfynd.xlsx
+++ b/artfynd/A 26849-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3786934</v>
+        <v>2278729</v>
       </c>
       <c r="B2" t="n">
-        <v>103345</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99010</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221423</v>
+        <v>219769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620864.5379703417</v>
+        <v>620865</v>
       </c>
       <c r="R2" t="n">
-        <v>6349685.779565657</v>
+        <v>6349686</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2009-06-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-06-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +770,21 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Tommy Knutsson, Lennart Johnsson, Ingrid Johnsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Lennart Johnsson, Ulla-Britt Andersson, Tommy Knutsson, Ingrid Johnsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2278729</v>
+        <v>60507195</v>
       </c>
       <c r="B3" t="n">
-        <v>96224</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +792,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219769</v>
+        <v>219797</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rosendal 800 m SV, Öl</t>
+          <t>Trankärrsbasen Venlinjen, Böda, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620864.5379703417</v>
+        <v>620967</v>
       </c>
       <c r="R3" t="n">
-        <v>6349685.779565657</v>
+        <v>6349604</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,22 +861,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-06-05</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-06-05</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett antal plantor i vägkanten på båda sidor längs Trankärrsbasen, 15-100 meter söder om korsningen Trankärrsbasen-Venlinjen</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,23 +893,128 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>blandskog barr/löv</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Karl Sandzén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Karl Sandzén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3786934</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106328</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rosendal 800 m SV, Öl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>620865</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6349686</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2009-06-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2009-06-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>blandskog barr/löv</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Thomas Gunnarsson, Lennart Johnsson, Ulla-Britt Andersson, Tommy Knutsson, Ingrid Johnsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Tommy Knutsson, Lennart Johnsson, Ingrid Johnsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26849-2026 artfynd.xlsx
+++ b/artfynd/A 26849-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2278729</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60507195</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,8 +1030,18 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3786934</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>